--- a/outputs/metrics/baseline_model_ranking.xlsx
+++ b/outputs/metrics/baseline_model_ranking.xlsx
@@ -607,43 +607,43 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0.41</v>
+        <v>0.4</v>
       </c>
       <c r="D4" t="n">
-        <v>0.7052117263843648</v>
+        <v>0.7100977198697068</v>
       </c>
       <c r="E4" t="n">
-        <v>0.615819209039548</v>
+        <v>0.6197183098591549</v>
       </c>
       <c r="F4" t="n">
-        <v>0.8288973384030418</v>
+        <v>0.8365019011406845</v>
       </c>
       <c r="G4" t="n">
-        <v>0.384180790960452</v>
+        <v>0.3802816901408451</v>
       </c>
       <c r="H4" t="n">
-        <v>0.706645056726094</v>
+        <v>0.7119741100323624</v>
       </c>
       <c r="I4" t="n">
-        <v>0.6125356125356125</v>
+        <v>0.6153846153846154</v>
       </c>
       <c r="J4" t="n">
-        <v>0.5463659147869674</v>
+        <v>0.5527638190954773</v>
       </c>
       <c r="K4" t="n">
-        <v>0.7971087495802325</v>
+        <v>0.7962421327440339</v>
       </c>
       <c r="L4" t="n">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="M4" t="n">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="N4" t="n">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="O4" t="n">
-        <v>218</v>
+        <v>220</v>
       </c>
     </row>
     <row r="5">
@@ -658,43 +658,43 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>0.41</v>
+        <v>0.4</v>
       </c>
       <c r="D5" t="n">
-        <v>0.7052117263843648</v>
+        <v>0.7100977198697068</v>
       </c>
       <c r="E5" t="n">
-        <v>0.615819209039548</v>
+        <v>0.6197183098591549</v>
       </c>
       <c r="F5" t="n">
-        <v>0.8288973384030418</v>
+        <v>0.8365019011406845</v>
       </c>
       <c r="G5" t="n">
-        <v>0.384180790960452</v>
+        <v>0.3802816901408451</v>
       </c>
       <c r="H5" t="n">
-        <v>0.706645056726094</v>
+        <v>0.7119741100323624</v>
       </c>
       <c r="I5" t="n">
-        <v>0.6125356125356125</v>
+        <v>0.6153846153846154</v>
       </c>
       <c r="J5" t="n">
-        <v>0.5463659147869674</v>
+        <v>0.5527638190954773</v>
       </c>
       <c r="K5" t="n">
-        <v>0.7971087495802325</v>
+        <v>0.7962421327440339</v>
       </c>
       <c r="L5" t="n">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="M5" t="n">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="N5" t="n">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="O5" t="n">
-        <v>218</v>
+        <v>220</v>
       </c>
     </row>
     <row r="6">
@@ -709,43 +709,43 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>0.49</v>
+        <v>0.48</v>
       </c>
       <c r="D6" t="n">
-        <v>0.7328990228013029</v>
+        <v>0.7280130293159609</v>
       </c>
       <c r="E6" t="n">
-        <v>0.671280276816609</v>
+        <v>0.6632653061224489</v>
       </c>
       <c r="F6" t="n">
-        <v>0.7376425855513308</v>
+        <v>0.7414448669201521</v>
       </c>
       <c r="G6" t="n">
-        <v>0.328719723183391</v>
+        <v>0.336734693877551</v>
       </c>
       <c r="H6" t="n">
-        <v>0.7028985507246377</v>
+        <v>0.7001795332136446</v>
       </c>
       <c r="I6" t="n">
-        <v>0.7293447293447294</v>
+        <v>0.717948717948718</v>
       </c>
       <c r="J6" t="n">
-        <v>0.5418994413407822</v>
+        <v>0.5386740331491713</v>
       </c>
       <c r="K6" t="n">
-        <v>0.7971087495802325</v>
+        <v>0.7962421327440339</v>
       </c>
       <c r="L6" t="n">
-        <v>256</v>
+        <v>252</v>
       </c>
       <c r="M6" t="n">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="N6" t="n">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="O6" t="n">
-        <v>194</v>
+        <v>195</v>
       </c>
     </row>
     <row r="7">
@@ -802,103 +802,103 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Random Forest</t>
+          <t>Logistic Regression</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>default_0_50</t>
+          <t>operational_from_validation</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>0.5</v>
+        <v>0.52</v>
       </c>
       <c r="D8" t="n">
-        <v>0.7312703583061889</v>
+        <v>0.7166123778501629</v>
       </c>
       <c r="E8" t="n">
-        <v>0.6788321167883211</v>
+        <v>0.6529209621993127</v>
       </c>
       <c r="F8" t="n">
-        <v>0.7072243346007605</v>
+        <v>0.7224334600760456</v>
       </c>
       <c r="G8" t="n">
-        <v>0.3211678832116788</v>
+        <v>0.3470790378006873</v>
       </c>
       <c r="H8" t="n">
-        <v>0.6927374301675978</v>
+        <v>0.6859205776173285</v>
       </c>
       <c r="I8" t="n">
-        <v>0.7492877492877493</v>
+        <v>0.7122507122507122</v>
       </c>
       <c r="J8" t="n">
-        <v>0.5299145299145299</v>
+        <v>0.521978021978022</v>
       </c>
       <c r="K8" t="n">
-        <v>0.7971087495802325</v>
+        <v>0.7849869465839048</v>
       </c>
       <c r="L8" t="n">
-        <v>263</v>
+        <v>250</v>
       </c>
       <c r="M8" t="n">
-        <v>88</v>
+        <v>101</v>
       </c>
       <c r="N8" t="n">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="O8" t="n">
-        <v>186</v>
+        <v>190</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Logistic Regression</t>
+          <t>Random Forest</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>operational_from_validation</t>
+          <t>default_0_50</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>0.52</v>
+        <v>0.5</v>
       </c>
       <c r="D9" t="n">
-        <v>0.7166123778501629</v>
+        <v>0.7214983713355049</v>
       </c>
       <c r="E9" t="n">
-        <v>0.6529209621993127</v>
+        <v>0.6678832116788321</v>
       </c>
       <c r="F9" t="n">
-        <v>0.7224334600760456</v>
+        <v>0.6958174904942965</v>
       </c>
       <c r="G9" t="n">
-        <v>0.3470790378006873</v>
+        <v>0.3321167883211679</v>
       </c>
       <c r="H9" t="n">
-        <v>0.6859205776173285</v>
+        <v>0.6815642458100558</v>
       </c>
       <c r="I9" t="n">
-        <v>0.7122507122507122</v>
+        <v>0.7407407407407407</v>
       </c>
       <c r="J9" t="n">
-        <v>0.521978021978022</v>
+        <v>0.5169491525423728</v>
       </c>
       <c r="K9" t="n">
-        <v>0.7849869465839048</v>
+        <v>0.7962421327440339</v>
       </c>
       <c r="L9" t="n">
-        <v>250</v>
+        <v>260</v>
       </c>
       <c r="M9" t="n">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="N9" t="n">
-        <v>73</v>
+        <v>80</v>
       </c>
       <c r="O9" t="n">
-        <v>190</v>
+        <v>183</v>
       </c>
     </row>
     <row r="10">
